--- a/public/templates/examples/A-016-IncidentNotificationEscalationContactList-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-016-IncidentNotificationEscalationContactList-EXAMPLE-L.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -216,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -287,6 +290,10 @@
     <xf numFmtId="164" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -758,7 +765,7 @@
       <c r="G6" s="23" t="n"/>
       <c r="H6" s="22" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Review cadence</t>
@@ -786,7 +793,7 @@
     <row r="10" ht="27.75" customHeight="1">
       <c r="A10" s="9" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
           <t>ID</t>
@@ -828,7 +835,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
           <t>CN-001</t>
@@ -868,7 +875,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
           <t>CN-002</t>
@@ -908,7 +915,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
           <t>CN-003</t>
@@ -948,7 +955,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
         <is>
           <t>CN-004</t>
@@ -1028,7 +1035,7 @@
         <v>46028</v>
       </c>
     </row>
-    <row r="17" ht="19.5" customHeight="1">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
         <is>
           <t>CN-006</t>
@@ -1068,7 +1075,7 @@
         <v>45810</v>
       </c>
     </row>
-    <row r="18" ht="19.5" customHeight="1">
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
           <t>CN-007</t>
@@ -1201,7 +1208,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Summary (as of 2026-06-03)</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1221,6 @@
       <c r="B24" s="26" t="n"/>
       <c r="C24" s="13">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1225,8 +1231,7 @@
       </c>
       <c r="B25" s="26" t="n"/>
       <c r="C25" s="13">
-        <f>COUNTIFS(A12:A21,"&lt;&gt;",H12:H21,"&gt;="&amp;(TODAY()-365))</f>
-        <v/>
+        <f>COUNTIFS(A12:A21,"&lt;&gt;",H12:H21,"&gt;="&amp;(DATE(2026,6,3)-365))</f>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -1237,8 +1242,7 @@
       </c>
       <c r="B26" s="26" t="n"/>
       <c r="C26" s="13">
-        <f>COUNTIFS(A12:A21,"&lt;&gt;",H12:H21,"&lt;"&amp;(TODAY()-365))</f>
-        <v/>
+        <f>COUNTIFS(A12:A21,"&lt;&gt;",H12:H21,"&lt;"&amp;(DATE(2026,6,3)-365))</f>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -1250,7 +1254,6 @@
       <c r="B27" s="26" t="n"/>
       <c r="C27" s="13">
         <f>COUNTIFS(A12:A21,"&lt;&gt;",H12:H21,"")</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -1349,13 +1352,11 @@
           <t>/s/ Dr. Lisa Park</t>
         </is>
       </c>
-      <c r="D40" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1">
+      <c r="D40" s="29">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="41" ht="50.5" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
         <is>
           <t>Information Security Analyst</t>
@@ -1371,10 +1372,8 @@
           <t>/s/ Raymond Osei</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="D41" s="29">
+        <v>46034</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
@@ -1409,16 +1408,14 @@
       <c r="F44" s="14" t="n"/>
       <c r="G44" s="14" t="n"/>
     </row>
-    <row r="45" ht="17" customHeight="1">
+    <row r="45" ht="34.7" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="B45" s="28">
+        <v>46034</v>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
@@ -1434,11 +1431,11 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="12" t="n"/>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="2" t="n"/>
+    <row r="47">
+      <c r="A47"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A36:H36"/>
@@ -1453,7 +1450,6 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A47:H47"/>
     <mergeCell ref="C3:H3"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A32:H32"/>
@@ -1470,14 +1466,8 @@
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="E12:E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
-      <formula1>"Active,Under Review,Retired,Decommissioned"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>